--- a/AMAS Standards List Data.xlsx
+++ b/AMAS Standards List Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lrosenth/amas-tech-reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841D175F-382A-AF4A-AE60-DDA9862EF6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2F6512-7DB3-1D49-B41F-FA6A84888F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61240" yWindow="1860" windowWidth="37160" windowHeight="21100" xr2:uid="{98DD96FF-909E-BB43-A3CF-B6AA999C76C6}"/>
+    <workbookView xWindow="60800" yWindow="4200" windowWidth="38440" windowHeight="25800" xr2:uid="{98DD96FF-909E-BB43-A3CF-B6AA999C76C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="204">
   <si>
     <t>SDO/Group</t>
   </si>
@@ -45,18 +45,6 @@
     <t>C2PA</t>
   </si>
   <si>
-    <t>Content Credentials</t>
-  </si>
-  <si>
-    <t>ISO TC 171/SC 2</t>
-  </si>
-  <si>
-    <t>ISO 22144</t>
-  </si>
-  <si>
-    <t>https://www.iso.org/standard/90726.html</t>
-  </si>
-  <si>
     <t>ISO/IEC JTC 1/SC 29/WG 1</t>
   </si>
   <si>
@@ -69,15 +57,6 @@
     <t>https://originator-profile.org/en-US/</t>
   </si>
   <si>
-    <t>Open Provenance</t>
-  </si>
-  <si>
-    <t>PROV</t>
-  </si>
-  <si>
-    <t>https://openprovenance.org/</t>
-  </si>
-  <si>
     <t>Trust and Authenticity</t>
   </si>
   <si>
@@ -135,9 +114,6 @@
     <t>IWA 44</t>
   </si>
   <si>
-    <t>Unique Media Identifier (UMid)</t>
-  </si>
-  <si>
     <t>W3C</t>
   </si>
   <si>
@@ -171,30 +147,15 @@
     <t>https://www.w3.org/ns/tdmrep/</t>
   </si>
   <si>
-    <t>Spawning</t>
-  </si>
-  <si>
-    <t>Spawning ai.txt</t>
-  </si>
-  <si>
-    <t>https://spawning.ai/ai-txt</t>
-  </si>
-  <si>
     <t>IETF</t>
   </si>
   <si>
     <t>RFC 9309</t>
   </si>
   <si>
-    <t>Robots.txt</t>
-  </si>
-  <si>
     <t>https://datatracker.ietf.org/doc/html/rfc9309</t>
   </si>
   <si>
-    <t>Vocabulary for Expressing Content Preferences for AI Training</t>
-  </si>
-  <si>
     <t>Watermarking</t>
   </si>
   <si>
@@ -213,9 +174,6 @@
     <t>ITU-T SG17</t>
   </si>
   <si>
-    <t>2413-PLEN</t>
-  </si>
-  <si>
     <t>X.ig-dw: Implementation guidelines for digital watermarking</t>
   </si>
   <si>
@@ -231,21 +189,6 @@
     <t>https://www.iso.org/standard/84956.html</t>
   </si>
   <si>
-    <t>NIH</t>
-  </si>
-  <si>
-    <t>A Review of Medical Image Watermarking Requirements for Teleradiology</t>
-  </si>
-  <si>
-    <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3597963/</t>
-  </si>
-  <si>
-    <t>ISO/IEC JTC 1/SC 29/WG 11</t>
-  </si>
-  <si>
-    <t>ISO/IEC TR 21000-11:2004</t>
-  </si>
-  <si>
     <t>IEEE</t>
   </si>
   <si>
@@ -255,9 +198,6 @@
     <t>https://standards.ieee.org/ieee/3361/11224/</t>
   </si>
   <si>
-    <t>https://www.iso.org/standard/40487.html</t>
-  </si>
-  <si>
     <t>https://store.accuristech.com/standards/ieee-p3152?product_id=2918804</t>
   </si>
   <si>
@@ -324,24 +264,12 @@
     <t>Web pages</t>
   </si>
   <si>
-    <t>Umid</t>
-  </si>
-  <si>
-    <t>ietf-aipref-vocab-00</t>
-  </si>
-  <si>
-    <t>https://www.ietf.org/archive/id/draft-ietf-aipref-vocab-00.html</t>
-  </si>
-  <si>
     <t>Audio</t>
   </si>
   <si>
     <t>Published, but temporary</t>
   </si>
   <si>
-    <t>Medical Image Watermarking</t>
-  </si>
-  <si>
     <t>Video</t>
   </si>
   <si>
@@ -357,9 +285,6 @@
     <t>JVET (ITU-T SG21 &amp; ISO/IEC JTC 1/SC 29/ WG5)</t>
   </si>
   <si>
-    <t>https://www.itu.int/itu-t/workprog/wp_item.aspx?isn=21058</t>
-  </si>
-  <si>
     <t>ITU-T SG21/Q7</t>
   </si>
   <si>
@@ -396,21 +321,9 @@
     <t>This standard addresses recognizable audio and visual markers that assist humans in distinguishing communication with a human, a machine, or a combination of both. Therefore, the standard defines visual, textual, and auditory marks. This standard does not cover methods to determine whether an interaction is with a machine, such as Turing tests.</t>
   </si>
   <si>
-    <t>This standard provides guidelines for embedding content credentials in digital media to ensure provenance. It outlines methods for attaching metadata to digital assets, which can include information about the creator, creation date, and any modifications made to the content. This helps in maintaining a verifiable record of the content's history.</t>
-  </si>
-  <si>
-    <t>This ISO standard outlines methods for documenting content credentials to maintain provenance. It specifies the types of metadata that should be included and the formats for storing this information. By following these guidelines, organizations can ensure that their digital content is traceable and its authenticity can be verified.</t>
-  </si>
-  <si>
-    <t>This standard is planned to provide an overview of mechanisms used for watermarking of media assets.</t>
-  </si>
-  <si>
     <t>This specification provides a framework for documenting the origin of digital content. It includes guidelines for creating and maintaining profiles that capture detailed information about the content's creator and its creation process. This helps in establishing a clear and verifiable record of the content's provenance.</t>
   </si>
   <si>
-    <t>This standard offers a model for representing provenance information in digital content. It defines a set of concepts and relationships that can be used to describe the history of a digital asset, including its creation, modification, and distribution. This model can be applied across various types of digital content, providing a flexible and comprehensive approach to provenance documentation.</t>
-  </si>
-  <si>
     <t>This standard offers an overview of trustworthiness in artificial intelligence. It provides guidelines for assessing the reliability and integrity of AI systems, ensuring that they produce trustworthy results. This is crucial in applications where AI is used to generate or manipulate digital content, as it helps in maintaining the authenticity of the output.</t>
   </si>
   <si>
@@ -429,9 +342,6 @@
     <t>This protocol provides guidelines for reserving content from text and data mining. It includes methods for creating and maintaining TDMRep files, which can be used to document the reservation of digital assets. This helps in ensuring that content is not used for data mining without the creator's consent.</t>
   </si>
   <si>
-    <t>This specification offers a method for opting out of AI training. It includes guidelines for creating and maintaining ai.txt files, which can be used to document the opt-out of digital assets. This helps in ensuring that content is not used for AI training without the creator's consent.</t>
-  </si>
-  <si>
     <t>This standard provides guidelines for excluding content from web crawlers. It includes methods for creating and maintaining robots.txt files, which can be used to document the exclusion of digital assets. This helps in ensuring that content is not accessed by web crawlers without the creator's consent.</t>
   </si>
   <si>
@@ -445,12 +355,6 @@
   </si>
   <si>
     <t>This standard provides an overview of DRM technologies for digital publications. It includes guidelines for creating and maintaining DRM files, which can be used to document the DRM of digital assets. This helps in ensuring that content is properly accounted for and can be easily identified and retrieved.</t>
-  </si>
-  <si>
-    <t>This review outlines the requirements for watermarking medical images for teleradiology. It includes guidelines for creating and maintaining watermark files, which can be used to document the watermarking of medical images. This helps in ensuring that content is properly accounted for and can be easily identified and retrieved.</t>
-  </si>
-  <si>
-    <t>This standard provides tools for evaluating persistent association technologies. It includes guidelines for creating and maintaining evaluation files, which can be used to document the evaluation of digital assets. This helps in ensuring that content is properly accounted for and can be easily identified and retrieved.</t>
   </si>
   <si>
     <t>This draft standard offers methods for evaluating the robustness of digital watermarking. It includes guidelines for creating and maintaining evaluation files, which can be used to document the evaluation of digital assets. This helps in ensuring that content is properly accounted for and can be easily identified and retrieved.</t>
@@ -504,9 +408,6 @@
     <t>This standard focuses on trust and authenticity in JPEG images through provenance, detection and fact-checking. It provides a framework for embedding metadata directly into JPEG files in the form of trust indicators. This allows users to decide the degree of trust they can put on a digital assets as a function of their trust profiles. This is particularly useful in contexts where image manipulation is common, such as in social media applications.</t>
   </si>
   <si>
-    <t>This standard introduces a series of trust profile snippets that can be used either as is or as starting points to establish profiles for use in specific workflows, use cases and applications such as broadcasting, digital cameras, AI-powered content generation services, etc.</t>
-  </si>
-  <si>
     <t>This specification provides a framework for expressing metadata that captures detailed information about the content, including ownership and authorship.</t>
   </si>
   <si>
@@ -526,9 +427,6 @@
   </si>
   <si>
     <t>https://www.iptc.org/std/photometadata/specification/IPTC-PhotoMetadata</t>
-  </si>
-  <si>
-    <t>IPTC Photo Metadata Standard 2024.1</t>
   </si>
   <si>
     <t>This document specifies metadata properties with a focus on usage with photos, some of these properties are also specified by the IPTC Video Metadata Hub.</t>
@@ -561,10 +459,6 @@
 PDF</t>
   </si>
   <si>
-    <t>Audio
-Video</t>
-  </si>
-  <si>
     <t>Images
 Audio</t>
   </si>
@@ -576,13 +470,7 @@
     <t>Date of Publication</t>
   </si>
   <si>
-    <t>https://c2pa.org/specifications/specifications/2.2/specs/C2PA_Specification.html</t>
-  </si>
-  <si>
     <t>ISO 24138:2024</t>
-  </si>
-  <si>
-    <t>https://www.din.de/resource/blob/1189854/d8282af953803e9ca844c02f468e151c/iwa-44-draft-public-consultation-data.pdf</t>
   </si>
   <si>
     <t>Overview of trustworthiness in artificial intelligence</t>
@@ -592,9 +480,6 @@
 Part 1: Overview of copyright protection technologies in use in the publishing industry</t>
   </si>
   <si>
-    <t>MPEG-21 — Part 11: Evaluation Tools for Persistent Association Technologies</t>
-  </si>
-  <si>
     <t>DASH - Part 4: Segment Encryption and Authentication</t>
   </si>
   <si>
@@ -614,10 +499,6 @@
 Robustness of Digital Watermarking Implementation in Digital Contents</t>
   </si>
   <si>
-    <t>Recommended Practices for 
-Levels of Artificial Intelligence Generated Content Technologies</t>
-  </si>
-  <si>
     <t>H.MMAUTH: 
 Framework for authentication of multimedia content</t>
   </si>
@@ -631,13 +512,169 @@
   </si>
   <si>
     <t>Any (image focused)</t>
+  </si>
+  <si>
+    <t>Recommended Practices for  Levels of Artificial Intelligence Generated Content Technologies</t>
+  </si>
+  <si>
+    <t>SG17-TD42/WP4</t>
+  </si>
+  <si>
+    <t>Robots Exclusion Protocol</t>
+  </si>
+  <si>
+    <t>https://c2pa.org/specifications/specifications/2.4/specs/C2PA_Specification.html</t>
+  </si>
+  <si>
+    <t>This standard focuses on providing a tamper-evident provenance record, called a Content Credential, that can be embedded into digital media, watermarked or stored online.  A Content Credential can include information about the creator, creation date, and any modifications made to the content. This helps in maintaining a verifiable record of the content's history.</t>
+  </si>
+  <si>
+    <t>This standard introduces trust indicator sets, trust profiles and trust reports that can be used to in specific workflows, use cases and applications such as broadcasting, digital cameras, AI-powered content generation services, etc.</t>
+  </si>
+  <si>
+    <t>This standard provides an overview of mechanisms used for watermarking of media assets.</t>
+  </si>
+  <si>
+    <t>https://www.iso.org/standard/89038.html</t>
+  </si>
+  <si>
+    <t>https://www.iso.org/standard/90209.html</t>
+  </si>
+  <si>
+    <t>IPTC Photo Metadata Standard 2025.1</t>
+  </si>
+  <si>
+    <t>Global Media Identifier (GMI)</t>
+  </si>
+  <si>
+    <t>GMI</t>
+  </si>
+  <si>
+    <t>https://www.iso.org/standard/88469.html</t>
+  </si>
+  <si>
+    <t>https://www.ietf.org/archive/id/draft-ietf-aipref-vocab-06.html</t>
+  </si>
+  <si>
+    <t>draft-ietf-aipref-vocab-06</t>
+  </si>
+  <si>
+    <t>Vocabulary for expressing AI usage preferences</t>
+  </si>
+  <si>
+    <t>CAWG Identity Assertion Specification</t>
+  </si>
+  <si>
+    <t>Creation Assertions Working Group (DIF)</t>
+  </si>
+  <si>
+    <t>CAWG Identity Assertion v1.2</t>
+  </si>
+  <si>
+    <t>https://cawg.io/identity/1.2/</t>
+  </si>
+  <si>
+    <t>This specification enables content creators to cryptographically bind their verified identity to C2PA-signed digital assets. It supports multiple identity binding methods including X.509 certificates and Identity Claim Aggregators (ICA). Ratified by the Decentralized Identity Foundation (DIF) on December 15, 2025, after CAWG formally became a DIF working group in March 2025. Directly extends and complements the C2PA Specification and CAWG Metadata specification.</t>
+  </si>
+  <si>
+    <t>W3C Verifiable Credentials Data Model v2.0</t>
+  </si>
+  <si>
+    <t>VC Data Model 2.0</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/TR/vc-data-model-2.0/</t>
+  </si>
+  <si>
+    <t>This W3C Recommendation (published May 15, 2025) provides a standard data model for cryptographically secure, privacy-respecting, machine-verifiable credentials. It is directly applicable to content authenticity workflows ‚Äî notably as the foundation for identity binding in CAWG Identity Assertions. The v2.0 family comprises seven interlocking specifications covering the data model, JSON-LD contexts, and securing mechanisms (ECDSA and BBS). Supersedes v1.1.</t>
+  </si>
+  <si>
+    <t>NIST AI 100-4: Reducing Risks Posed by Synthetic Content</t>
+  </si>
+  <si>
+    <t>NIST</t>
+  </si>
+  <si>
+    <t>NIST AI 100-4</t>
+  </si>
+  <si>
+    <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-4.pdf</t>
+  </si>
+  <si>
+    <t>Images
+Audio
+Video
+Any</t>
+  </si>
+  <si>
+    <t>This NIST technical report provides authoritative US government guidance on detecting, authenticating, and labeling AI-generated and synthetic content. It covers digital watermarking, metadata-based provenance, and content labeling approaches, with explicit interoperability references to C2PA and W3C PROV as recommended standards. Although a technical report rather than a normative standard, it carries significant influence on US policy and industry practice for AI content authenticity.</t>
+  </si>
+  <si>
+    <t>ISO/IEC 21000-3:2025</t>
+  </si>
+  <si>
+    <t>https://www.iso.org/standard/89735.html</t>
+  </si>
+  <si>
+    <t>This 2025 edition of MPEG-21 Part 3 replaces the original 2003 version and defines a framework for the unique identification of digital items and their components. It provides persistent, globally unique identifiers for digital content objects and is applicable across audio, video, images, and documents. Relevant to asset identifier workflows and interoperable with C2PA, ISCC, and GMI (IWA 44) identification schemes.</t>
+  </si>
+  <si>
+    <t>Content Credentials (C2PA)</t>
+  </si>
+  <si>
+    <t>MPEG-21 Part 3: Digital Item Identification</t>
+  </si>
+  <si>
+    <t>Chinese National Standard</t>
+  </si>
+  <si>
+    <t>GB 45438</t>
+  </si>
+  <si>
+    <t>Images
+Audio
+Video</t>
+  </si>
+  <si>
+    <t>This document defines the compulsory technical methods for explicit and implicit marking of AI-generated text, images, audio, and video.</t>
+  </si>
+  <si>
+    <t>https://openstd.samr.gov.cn/bzgk/std/newGbInfo?hcno=F32EA2A561F1886CD8D606513512D547</t>
+  </si>
+  <si>
+    <t>ITU-T X.2210</t>
+  </si>
+  <si>
+    <t>https://www.itu.int/md/T25-SG17-R-0030</t>
+  </si>
+  <si>
+    <t>Cybersecurity technology—Labeling method for content generated by artificial intelligence</t>
+  </si>
+  <si>
+    <t>https://www.itu.int/itu-t/workprog/wp_item.aspx?isn=21058</t>
+  </si>
+  <si>
+    <t>This report will provide an end-to-end framework for multimedia authentication for various use cases such as broadcast, broadband distributions and live/low latency/on-demand streaming, real-time communication, ingesting the content for production and consumption by professional and public consumers. The framework will describe the workflows for various use cases, the role of each actor and entity, the interface requirement between various entities, and the requirements for each entity’s functionalities and features.</t>
+  </si>
+  <si>
+    <t>https://www.itu.int/ITU-T/workprog/wp_item.aspx?isn=23647</t>
+  </si>
+  <si>
+    <t>HSTP-MMAuth:
+Multimedia authentication framework, workflows and procedures</t>
+  </si>
+  <si>
+    <t>ITU-T SG21</t>
+  </si>
+  <si>
+    <t>HSTP-MMAuth</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -668,16 +705,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -694,12 +745,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -714,6 +791,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1052,7 +1138,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.83203125" style="4" customWidth="1"/>
@@ -1072,7 +1158,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
@@ -1084,186 +1170,192 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="80" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="G2" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="100" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="4">
         <v>2025</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="4" t="s">
+      <c r="H3" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="20" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="4">
+        <v>2025</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="80" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="4" t="s">
+    <row r="7" spans="1:9" ht="80" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="B7" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="100" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G4" s="4">
-        <v>2025</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="40" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="F7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G7" s="4">
-        <v>2025</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="I7" s="4" t="s">
-        <v>155</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="80" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>11</v>
@@ -1272,21 +1364,21 @@
         <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>97</v>
+        <v>64</v>
+      </c>
+      <c r="G8" s="4">
+        <v>2020</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="100" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="80" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>145</v>
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>13</v>
@@ -1295,27 +1387,24 @@
         <v>14</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="G9" s="4">
-        <v>2013</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>85</v>
+        <v>2018</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="80" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>17</v>
@@ -1323,25 +1412,25 @@
       <c r="D10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="5" t="s">
         <v>19</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G10" s="4">
-        <v>2020</v>
+        <v>73</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="80" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>20</v>
@@ -1350,710 +1439,764 @@
         <v>21</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G11" s="4">
-        <v>2018</v>
+        <v>73</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="80" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>149</v>
+      <c r="B12" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>25</v>
+        <v>141</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>93</v>
+        <v>64</v>
+      </c>
+      <c r="G12" s="4">
+        <v>2024</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="80" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>28</v>
+        <v>164</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="4">
+        <v>2025</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="80" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="D14" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="G14" s="4">
         <v>2024</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>85</v>
+      <c r="H14" s="4" t="s">
+        <v>136</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="80" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>35</v>
+        <v>156</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>30</v>
+        <v>118</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>178</v>
+        <v>40</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="G15" s="4">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="80" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="80" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="B17" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G16" s="4">
-        <v>2024</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="G17" s="4">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="80" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>150</v>
+        <v>42</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>53</v>
+        <v>155</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
+      </c>
+      <c r="G18" s="4">
+        <v>2024</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="80" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>54</v>
+        <v>143</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>100</v>
+        <v>51</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>85</v>
+        <v>64</v>
+      </c>
+      <c r="G19" s="4">
+        <v>2024</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="80" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="140" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" s="6"/>
+    </row>
+    <row r="22" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="B22" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" s="1">
+        <v>2026</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="K22" s="6"/>
+    </row>
+    <row r="23" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="K23" s="6"/>
+    </row>
+    <row r="24" spans="1:11" ht="140" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="160" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="4">
+        <v>2024</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="100" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" s="4">
+        <v>2024</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="80" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G20" s="4">
-        <v>2020</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="80" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G21" s="4">
+      <c r="F27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G27" s="4">
         <v>2024</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H27" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G28" s="4">
+        <v>2025</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="80" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G29" s="4">
+        <v>2018</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G30" s="4">
+        <v>2023</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" customFormat="1" ht="85" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>170</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" t="s">
+        <v>171</v>
+      </c>
+      <c r="D31" t="s">
+        <v>172</v>
+      </c>
+      <c r="E31" t="s">
+        <v>173</v>
+      </c>
+      <c r="F31" t="s">
+        <v>64</v>
+      </c>
+      <c r="G31">
+        <v>2025</v>
+      </c>
+      <c r="H31" t="s">
+        <v>65</v>
+      </c>
+      <c r="I31" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="80" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+    </row>
+    <row r="32" spans="1:11" customFormat="1" ht="85" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>175</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" t="s">
+        <v>176</v>
+      </c>
+      <c r="E32" t="s">
+        <v>177</v>
+      </c>
+      <c r="F32" t="s">
+        <v>64</v>
+      </c>
+      <c r="G32">
+        <v>2025</v>
+      </c>
+      <c r="H32" t="s">
+        <v>65</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" customFormat="1" ht="85" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>179</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C33" t="s">
         <v>180</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="D33" t="s">
+        <v>181</v>
+      </c>
+      <c r="E33" t="s">
+        <v>182</v>
+      </c>
+      <c r="F33" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="G33">
+        <v>2024</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>189</v>
+      </c>
+      <c r="B34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" t="s">
+        <v>130</v>
+      </c>
+      <c r="D34" t="s">
+        <v>185</v>
+      </c>
+      <c r="E34" t="s">
+        <v>186</v>
+      </c>
+      <c r="F34" t="s">
+        <v>64</v>
+      </c>
+      <c r="G34">
+        <v>2025</v>
+      </c>
+      <c r="H34" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G22" s="4">
-        <v>2024</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="80" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G23" s="4">
-        <v>2012</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="80" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G24" s="4">
-        <v>2004</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="80" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="I34" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="1" t="s">
+    </row>
+    <row r="35" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G35" s="4">
+        <v>2025</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="20" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="140" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="K26" s="6"/>
-    </row>
-    <row r="27" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K27" s="6"/>
-    </row>
-    <row r="28" spans="1:11" ht="120" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="K28" s="6"/>
-    </row>
-    <row r="29" spans="1:11" ht="140" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="160" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G30" s="4">
-        <v>2024</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="100" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G31" s="4">
-        <v>2024</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="80" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" s="1" t="s">
+    </row>
+    <row r="37" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G32" s="4">
-        <v>2024</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G33" s="4">
-        <v>2024</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="80" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G34" s="4">
-        <v>2018</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="120" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G35" s="4">
-        <v>2023</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>169</v>
+      <c r="H37" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E14" r:id="rId1" xr:uid="{1C2DF84F-92F6-C344-BC25-589FEED15782}"/>
-    <hyperlink ref="E12" r:id="rId2" xr:uid="{D60985A3-FC71-4B53-89E5-8B788CDF5E07}"/>
-    <hyperlink ref="E13" r:id="rId3" location="heading=h.40o7mijeapa7" xr:uid="{6AAEFA71-EE57-4973-A27B-C9B27F385D79}"/>
-    <hyperlink ref="E19" r:id="rId4" xr:uid="{F799D523-0062-4E59-AC23-DF6B0B92245B}"/>
-    <hyperlink ref="E29" r:id="rId5" xr:uid="{09351161-5899-4D02-825D-687E82A106E5}"/>
-    <hyperlink ref="E7" r:id="rId6" xr:uid="{5FC36867-5D0F-9B45-996C-E7F8638F1394}"/>
-    <hyperlink ref="E31" r:id="rId7" xr:uid="{FFE2E8C6-B3CD-E348-A2D1-9D6058CD905A}"/>
-    <hyperlink ref="E24" r:id="rId8" xr:uid="{54861D70-135B-004D-94D3-2C23B69D89CD}"/>
-    <hyperlink ref="E34" r:id="rId9" xr:uid="{85B42C16-B96C-3141-8A42-740BB3AFB62A}"/>
-    <hyperlink ref="E2" r:id="rId10" xr:uid="{9DDF33E2-C7ED-6D47-8C71-91EC549D82B7}"/>
-    <hyperlink ref="E9" r:id="rId11" xr:uid="{93EC6724-26ED-7C4B-B28E-E129C84A4F9E}"/>
-    <hyperlink ref="E11" r:id="rId12" xr:uid="{FB82F7D5-D433-6343-A5C2-C9EDA89D41E5}"/>
-    <hyperlink ref="E15" r:id="rId13" xr:uid="{615C773A-227E-6543-A80E-EF1BB05D2E9F}"/>
-    <hyperlink ref="E21" r:id="rId14" xr:uid="{53472CDB-849E-A546-9880-9BF25B649BDD}"/>
-    <hyperlink ref="E23" r:id="rId15" xr:uid="{CD7E9D8A-A7C9-804C-893F-C8257BA934DC}"/>
+    <hyperlink ref="E12" r:id="rId1" xr:uid="{1C2DF84F-92F6-C344-BC25-589FEED15782}"/>
+    <hyperlink ref="E10" r:id="rId2" xr:uid="{D60985A3-FC71-4B53-89E5-8B788CDF5E07}"/>
+    <hyperlink ref="E11" r:id="rId3" location="heading=h.40o7mijeapa7" xr:uid="{6AAEFA71-EE57-4973-A27B-C9B27F385D79}"/>
+    <hyperlink ref="E16" r:id="rId4" xr:uid="{F799D523-0062-4E59-AC23-DF6B0B92245B}"/>
+    <hyperlink ref="E24" r:id="rId5" xr:uid="{09351161-5899-4D02-825D-687E82A106E5}"/>
+    <hyperlink ref="E6" r:id="rId6" xr:uid="{5FC36867-5D0F-9B45-996C-E7F8638F1394}"/>
+    <hyperlink ref="E26" r:id="rId7" xr:uid="{FFE2E8C6-B3CD-E348-A2D1-9D6058CD905A}"/>
+    <hyperlink ref="E29" r:id="rId8" xr:uid="{85B42C16-B96C-3141-8A42-740BB3AFB62A}"/>
+    <hyperlink ref="E2" r:id="rId9" xr:uid="{9DDF33E2-C7ED-6D47-8C71-91EC549D82B7}"/>
+    <hyperlink ref="E9" r:id="rId10" xr:uid="{FB82F7D5-D433-6343-A5C2-C9EDA89D41E5}"/>
+    <hyperlink ref="E18" r:id="rId11" xr:uid="{53472CDB-849E-A546-9880-9BF25B649BDD}"/>
+    <hyperlink ref="E36" r:id="rId12" xr:uid="{53B366C5-AEB7-CD4F-A80F-A9982840D2EA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="52" fitToHeight="3" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
@@ -2070,15 +2213,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Meeting_x0020_Date xmlns="43f3aac0-5e6c-4529-8eca-b318fd6f3bb1" xsi:nil="true"/>
-    <Source xmlns="43f3aac0-5e6c-4529-8eca-b318fd6f3bb1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BC603E13C3A73340A6732121C1853D0C" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a9cb6de74c33d4e3470966593f12d6e0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="43f3aac0-5e6c-4529-8eca-b318fd6f3bb1" xmlns:ns3="2828a09b-4f48-432d-9559-a1f724b08bae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c2d1b904aad086a408849faa6bfb2a80" ns2:_="" ns3:_="">
     <xsd:import namespace="43f3aac0-5e6c-4529-8eca-b318fd6f3bb1"/>
@@ -2237,6 +2371,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Meeting_x0020_Date xmlns="43f3aac0-5e6c-4529-8eca-b318fd6f3bb1" xsi:nil="true"/>
+    <Source xmlns="43f3aac0-5e6c-4529-8eca-b318fd6f3bb1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF031DC2-3F49-456B-8ACE-BC811F5E6293}">
   <ds:schemaRefs>
@@ -2246,16 +2389,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24240BB2-E93E-416C-84FF-0227B25E9DCD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="43f3aac0-5e6c-4529-8eca-b318fd6f3bb1"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAAAC215-9937-4C7B-B4BD-7F77D1E34F91}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2272,4 +2405,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24240BB2-E93E-416C-84FF-0227B25E9DCD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="43f3aac0-5e6c-4529-8eca-b318fd6f3bb1"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/AMAS Standards List Data.xlsx
+++ b/AMAS Standards List Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lrosenth/amas-tech-reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2F6512-7DB3-1D49-B41F-FA6A84888F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ABB3F6C-64F0-2548-9E20-7668D5D62EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60800" yWindow="4200" windowWidth="38440" windowHeight="25800" xr2:uid="{98DD96FF-909E-BB43-A3CF-B6AA999C76C6}"/>
+    <workbookView xWindow="58420" yWindow="3400" windowWidth="38440" windowHeight="25800" xr2:uid="{98DD96FF-909E-BB43-A3CF-B6AA999C76C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="222">
   <si>
     <t>SDO/Group</t>
   </si>
@@ -72,9 +72,6 @@
     <t>ITU-T</t>
   </si>
   <si>
-    <t>ITU-T Y.3054</t>
-  </si>
-  <si>
     <t>Framework for trust-based media services</t>
   </si>
   <si>
@@ -292,9 +289,6 @@
   </si>
   <si>
     <t>H.MMAUTH</t>
-  </si>
-  <si>
-    <t>H.274(V4)</t>
   </si>
   <si>
     <t>H.VADS</t>
@@ -642,9 +636,6 @@
     <t>https://openstd.samr.gov.cn/bzgk/std/newGbInfo?hcno=F32EA2A561F1886CD8D606513512D547</t>
   </si>
   <si>
-    <t>ITU-T X.2210</t>
-  </si>
-  <si>
     <t>https://www.itu.int/md/T25-SG17-R-0030</t>
   </si>
   <si>
@@ -668,13 +659,96 @@
   </si>
   <si>
     <t>HSTP-MMAuth</t>
+  </si>
+  <si>
+    <t>ITU-T Recommendation Y.3054</t>
+  </si>
+  <si>
+    <t>ITU-T Recommendation X.2210</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">This </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">Recommendation provides </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>guidelines for implementation of digital watermarking through a detailed methodology approach, including watermark preparation, embedding, distribution, and extraction. It targets a wide range of digital content carriers, including images, videos, files, and emerging artificial intelligence (AI) generated content</t>
+    </r>
+  </si>
+  <si>
+    <t>ITU-T Recommendation H.274(V4)</t>
+  </si>
+  <si>
+    <t>Open Binding of Content Identifiers - Resilient Layer (OBID-R)</t>
+  </si>
+  <si>
+    <t>SMPTE ST 2112-30:20xx</t>
+  </si>
+  <si>
+    <t>https://www.smpte.org/projects</t>
+  </si>
+  <si>
+    <t>This standard provides guidelines for binding content identifiers to digital media. It includes methods for creating and maintaining OBID files, which can be used to document the binding of digital assets. This helps in ensuring that content is properly accounted for and can be easily identified and retrieved</t>
+  </si>
+  <si>
+    <t>Descriptive Metadata Scheme for Identity and Integrity (DMS-II)</t>
+  </si>
+  <si>
+    <t>Audio
+Video
+Data</t>
+  </si>
+  <si>
+    <t>SMPTE ST 2140-1:20xx</t>
+  </si>
+  <si>
+    <t>SMPTE ST 2140-3:20xx</t>
+  </si>
+  <si>
+    <t>The DMS-II develops and documents an architecture, a data model and a detailed specification to carry Identity and Integrity metadata in SMPTE ST 377 Material Exchange Format (MXF) files using the SMPTE ST 336 KLV Protocol. The specification for bindings will address the MXF media structures including I frame and long GOP media, as well as Framewrapped, Clipwrapped and Partitioned files</t>
+  </si>
+  <si>
+    <t>This document defines the specifications for applying the JPEG Universal Metadata Box Format (JUMBF) data model for metadata to be carried in professional media files with reference to the SMPTE ST 2140-1 conceptual architecture for Identity and Integrity</t>
+  </si>
+  <si>
+    <t>Journalism Trust Initiative</t>
+  </si>
+  <si>
+    <t>Descriptive Metadata Scheme for Identity and Integrity JUMBF approach</t>
+  </si>
+  <si>
+    <t>CEN-CENELEC</t>
+  </si>
+  <si>
+    <t>CWA 17493 WORKSHOP AGREEMENT</t>
+  </si>
+  <si>
+    <t>https://www.cencenelec.eu/media/CEN-CENELEC/CWAs/ICT/cwa17493.pdf</t>
+  </si>
+  <si>
+    <t>This standard introduces a benchmark applicable to any type of news media outlets (television, radio, print and digital) to assess their efforts in terms of transparency, governance, editorial processes and responsibility policies, including in the usage of AI</t>
+  </si>
+  <si>
+    <t>SG17-TD308/WP4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -712,6 +786,33 @@
       <name val="Aptos Display"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF0F4761"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color rgb="FF212121"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color rgb="FF212121"/>
+      <name val="Google Sans Text"/>
     </font>
   </fonts>
   <fills count="3">
@@ -776,7 +877,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -799,6 +900,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1138,13 +1251,13 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19"/>
   <cols>
-    <col min="1" max="1" width="53.83203125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="56" style="4" customWidth="1"/>
     <col min="2" max="2" width="23.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="47.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="31.1640625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="34.5" style="4" customWidth="1"/>
     <col min="5" max="5" width="114" style="1" customWidth="1"/>
     <col min="6" max="6" width="25.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="31.1640625" style="4" customWidth="1"/>
@@ -1153,12 +1266,12 @@
     <col min="10" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="20">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
@@ -1170,79 +1283,79 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="80" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:9" ht="80">
       <c r="A2" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2" s="4">
         <v>2026</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="100" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="100">
       <c r="A3" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3" s="4">
         <v>2025</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="60">
       <c r="A4" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>9</v>
@@ -1251,82 +1364,82 @@
         <v>5</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="20" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="20">
       <c r="A5" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="60">
       <c r="A6" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G6" s="4">
         <v>2025</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="80" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="80">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>7</v>
@@ -1338,18 +1451,18 @@
         <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="80" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="80">
       <c r="A8" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>9</v>
@@ -1364,18 +1477,18 @@
         <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G8" s="4">
         <v>2020</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="80" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="80">
       <c r="A9" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>9</v>
@@ -1384,803 +1497,916 @@
         <v>13</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>14</v>
+        <v>201</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G9" s="4">
         <v>2018</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="80" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="80">
       <c r="A10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="80" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="80">
       <c r="A11" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="60">
+      <c r="A12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="C12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G12" s="4">
         <v>2024</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="60">
       <c r="A13" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>166</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G13" s="4">
         <v>2025</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="80" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="80">
       <c r="A14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G14" s="4">
         <v>2024</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="80" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="80">
       <c r="A15" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G15" s="4">
         <v>2022</v>
       </c>
       <c r="H15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="18" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="H16" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="80" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="80">
       <c r="A17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G17" s="4">
         <v>2020</v>
       </c>
       <c r="H17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="80">
+      <c r="A18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="80" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="G18" s="4">
         <v>2024</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="80" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="80">
       <c r="A19" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G19" s="4">
         <v>2024</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="80" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="80">
       <c r="A20" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="140" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="140">
       <c r="A21" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="F21" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="60">
       <c r="A22" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>88</v>
+        <v>204</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G22" s="1">
         <v>2026</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="120">
       <c r="A23" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="F23" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K23" s="6"/>
     </row>
-    <row r="24" spans="1:11" ht="140" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="140">
       <c r="A24" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="F24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="160">
+      <c r="A25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="160" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="E25" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="F25" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G25" s="4">
         <v>2024</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="100" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="100">
       <c r="A26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>35</v>
-      </c>
       <c r="F26" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G26" s="4">
         <v>2024</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="80" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="80">
       <c r="A27" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G27" s="4">
         <v>2024</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="60">
       <c r="A28" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G28" s="4">
         <v>2025</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="80" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="80">
       <c r="A29" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G29" s="4">
         <v>2018</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="120">
       <c r="A30" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G30" s="4">
         <v>2023</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" customFormat="1" ht="85" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" customFormat="1" ht="85">
       <c r="A31" t="s">
+        <v>168</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C31" t="s">
+        <v>169</v>
+      </c>
+      <c r="D31" t="s">
         <v>170</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="E31" t="s">
         <v>171</v>
       </c>
-      <c r="D31" t="s">
-        <v>172</v>
-      </c>
-      <c r="E31" t="s">
-        <v>173</v>
-      </c>
       <c r="F31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G31">
         <v>2025</v>
       </c>
       <c r="H31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" customFormat="1" ht="85" x14ac:dyDescent="0.2">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" customFormat="1" ht="85">
       <c r="A32" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E32" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G32">
         <v>2025</v>
       </c>
       <c r="H32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I32" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" customFormat="1" ht="85">
+      <c r="A33" t="s">
+        <v>177</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" customFormat="1" ht="85" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="D33" t="s">
         <v>179</v>
       </c>
-      <c r="B33" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="E33" t="s">
         <v>180</v>
       </c>
-      <c r="D33" t="s">
-        <v>181</v>
-      </c>
-      <c r="E33" t="s">
-        <v>182</v>
-      </c>
       <c r="F33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G33">
         <v>2024</v>
       </c>
       <c r="H33" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" customFormat="1" ht="68">
+      <c r="A34" t="s">
+        <v>187</v>
+      </c>
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" t="s">
         <v>183</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="E34" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" customFormat="1" ht="68" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>189</v>
-      </c>
-      <c r="B34" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" t="s">
-        <v>130</v>
-      </c>
-      <c r="D34" t="s">
-        <v>185</v>
-      </c>
-      <c r="E34" t="s">
-        <v>186</v>
-      </c>
       <c r="F34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G34">
         <v>2025</v>
       </c>
       <c r="H34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="60">
       <c r="A35" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G35" s="4">
         <v>2025</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I35" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="69">
+      <c r="A36" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E36" s="9" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" ht="20" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>196</v>
-      </c>
       <c r="F36" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="120">
       <c r="A37" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="52">
+      <c r="A38" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H37" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>199</v>
+      <c r="H38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="69">
+      <c r="A39" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="60">
+      <c r="A40" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="81">
+      <c r="A41" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G41" s="4">
+        <v>2019</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I41" s="16" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -2196,7 +2422,8 @@
     <hyperlink ref="E2" r:id="rId9" xr:uid="{9DDF33E2-C7ED-6D47-8C71-91EC549D82B7}"/>
     <hyperlink ref="E9" r:id="rId10" xr:uid="{FB82F7D5-D433-6343-A5C2-C9EDA89D41E5}"/>
     <hyperlink ref="E18" r:id="rId11" xr:uid="{53472CDB-849E-A546-9880-9BF25B649BDD}"/>
-    <hyperlink ref="E36" r:id="rId12" xr:uid="{53B366C5-AEB7-CD4F-A80F-A9982840D2EA}"/>
+    <hyperlink ref="E41" r:id="rId12" tooltip="Original URL:_x000a_https://www.cencenelec.eu/media/CEN-CENELEC/CWAs/ICT/cwa17493.pdf_x000a__x000a_Click to follow link." display="https://nam04.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.cencenelec.eu%2Fmedia%2FCEN-CENELEC%2FCWAs%2FICT%2Fcwa17493.pdf&amp;data=05%7C02%7Clrosenth%40adobe.com%7C71f3b8936e964811a28608decb9a7823%7Cfa7b1b5a7b34438794aed2c178decee1%7C0%7C0%7C639172061615839107%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=PlY4VJGxZd3n%2FaurLACIGYajW%2BThQ8db3mUsuGRuRsM%3D&amp;reserved=0" xr:uid="{81244181-B31C-4B44-83C8-A39137CB53AB}"/>
+    <hyperlink ref="D36" r:id="rId13" display="https://www.itu.int/md/T25-SG17-260601-TD-WP4-0308" xr:uid="{84C31C19-ABDB-5D43-A08F-028B7FE68E56}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="52" fitToHeight="3" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
